--- a/Training_Plan/RCP_Training_Plan_19-30_Oct_2026_KO.xlsx
+++ b/Training_Plan/RCP_Training_Plan_19-30_Oct_2026_KO.xlsx
@@ -1931,7 +1931,7 @@
       <c r="E16" s="17" t="n"/>
       <c r="F16" s="13" t="inlineStr">
         <is>
-          <t>박재민이 시험, 증빙, 보충 작업을 검토한 뒤 승인.</t>
+          <t>트레이너가 시험, 증빙, 보충 작업을 검토한 뒤 사인오프.</t>
         </is>
       </c>
     </row>
